--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -620,7 +620,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>assets/images/team/deepika-harkande.jpg</v>
       </c>
     </row>
     <row r="17">
@@ -628,7 +628,7 @@
         <v>Divya Chaudhari</v>
       </c>
       <c r="B17" t="str">
-        <v>Social Media Head</v>
+        <v>Social Media Lead</v>
       </c>
       <c r="C17" t="str">
         <v>Creative and Marketing Team</v>

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -760,7 +760,7 @@
         <v>Event Team</v>
       </c>
       <c r="D26" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/priyanka</v>
       </c>
     </row>
     <row r="27">
@@ -774,7 +774,7 @@
         <v>Event Team</v>
       </c>
       <c r="D27" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/vishal 1</v>
       </c>
     </row>
     <row r="28">
@@ -802,7 +802,7 @@
         <v>Event Team</v>
       </c>
       <c r="D29" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/rupali 1</v>
       </c>
     </row>
     <row r="30">
@@ -816,7 +816,7 @@
         <v>Event Team</v>
       </c>
       <c r="D30" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/ashish 1</v>
       </c>
     </row>
     <row r="31">

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -592,7 +592,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D14" t="str">
-        <v>assets/images/team/Aditi naik</v>
+        <v>assets/images/team/Aditi naik.jpeg</v>
       </c>
     </row>
     <row r="15">
@@ -620,7 +620,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D16" t="str">
-        <v>assets/images/team/smital</v>
+        <v>assets/images/team/smital.png</v>
       </c>
     </row>
     <row r="17">
@@ -634,7 +634,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D17" t="str">
-        <v>assets/images/team/divya</v>
+        <v>assets/images/team/divya.jpeg</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D18" t="str">
-        <v>assets/images/team/bhakti</v>
+        <v>assets/images/team/bhakti.png</v>
       </c>
     </row>
     <row r="19">
@@ -662,7 +662,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D19" t="str">
-        <v>assets/images/team/manasi</v>
+        <v>assets/images/team/manasi.jpeg</v>
       </c>
     </row>
     <row r="20">
@@ -704,7 +704,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D22" t="str">
-        <v>assets/images/team/rujuta</v>
+        <v>assets/images/team/rujuta.png</v>
       </c>
     </row>
     <row r="23">
@@ -718,7 +718,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D23" t="str">
-        <v>assets/images/team/vedant</v>
+        <v>assets/images/team/vedant.jpeg</v>
       </c>
     </row>
     <row r="24">
@@ -760,7 +760,7 @@
         <v>Event Team</v>
       </c>
       <c r="D26" t="str">
-        <v>assets/images/team/priyanka</v>
+        <v>assets/images/team/priyanka.jpg</v>
       </c>
     </row>
     <row r="27">
@@ -774,7 +774,7 @@
         <v>Event Team</v>
       </c>
       <c r="D27" t="str">
-        <v>assets/images/team/vishal 1</v>
+        <v>assets/images/team/vishal 1.png</v>
       </c>
     </row>
     <row r="28">
@@ -802,7 +802,7 @@
         <v>Event Team</v>
       </c>
       <c r="D29" t="str">
-        <v>assets/images/team/rupali 1</v>
+        <v>assets/images/team/rupali 1.png</v>
       </c>
     </row>
     <row r="30">
@@ -816,7 +816,7 @@
         <v>Event Team</v>
       </c>
       <c r="D30" t="str">
-        <v>assets/images/team/ashish 1</v>
+        <v>assets/images/team/ashish 1.png</v>
       </c>
     </row>
     <row r="31">

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -662,7 +662,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D19" t="str">
-        <v>assets/images/team/manasi.jpeg</v>
+        <v>assets/images/team/Manasi.jpeg</v>
       </c>
     </row>
     <row r="20">
@@ -704,7 +704,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D22" t="str">
-        <v>assets/images/team/rujuta.png</v>
+        <v>assets/images/team/Rujuta.png</v>
       </c>
     </row>
     <row r="23">

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -592,7 +592,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D14" t="str">
-        <v>assets/images/team/Aditi naik.jpeg</v>
+        <v>assets/images/team/Aditinaik.jpeg</v>
       </c>
     </row>
     <row r="15">
@@ -620,7 +620,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D16" t="str">
-        <v>assets/images/team/smital.png</v>
+        <v>assets/images/team/Smital.png</v>
       </c>
     </row>
     <row r="17">
@@ -774,7 +774,7 @@
         <v>Event Team</v>
       </c>
       <c r="D27" t="str">
-        <v>assets/images/team/vishal 1.png</v>
+        <v>assets/images/team/vishal1.png</v>
       </c>
     </row>
     <row r="28">
@@ -802,7 +802,7 @@
         <v>Event Team</v>
       </c>
       <c r="D29" t="str">
-        <v>assets/images/team/rupali 1.png</v>
+        <v>assets/images/team/rupali1.png</v>
       </c>
     </row>
     <row r="30">
@@ -816,7 +816,7 @@
         <v>Event Team</v>
       </c>
       <c r="D30" t="str">
-        <v>assets/images/team/ashish 1.png</v>
+        <v>assets/images/team/ashish1.png</v>
       </c>
     </row>
     <row r="31">

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -592,7 +592,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D14" t="str">
-        <v>assets/images/team/Aditinaik.jpeg</v>
+        <v>assets/images/team/Aditinaik.jpg</v>
       </c>
     </row>
     <row r="15">
@@ -774,7 +774,7 @@
         <v>Event Team</v>
       </c>
       <c r="D27" t="str">
-        <v>assets/images/team/vishal1.png</v>
+        <v>assets/images/team/vishal.jpg</v>
       </c>
     </row>
     <row r="28">
@@ -802,7 +802,7 @@
         <v>Event Team</v>
       </c>
       <c r="D29" t="str">
-        <v>assets/images/team/rupali1.png</v>
+        <v>assets/images/team/rupali.jpg</v>
       </c>
     </row>
     <row r="30">
@@ -816,7 +816,7 @@
         <v>Event Team</v>
       </c>
       <c r="D30" t="str">
-        <v>assets/images/team/ashish1.png</v>
+        <v>assets/images/team/ashish.jpg</v>
       </c>
     </row>
     <row r="31">

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -774,7 +774,7 @@
         <v>Event Team</v>
       </c>
       <c r="D27" t="str">
-        <v>assets/images/team/vishal.jpg</v>
+        <v>assets/images/team/Vishal.jpg</v>
       </c>
     </row>
     <row r="28">

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -592,7 +592,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D14" t="str">
-        <v>assets/images/team/Aditinaik.jpg</v>
+        <v>assets/images/team/AditiNaik.jpg</v>
       </c>
     </row>
     <row r="15">

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -564,7 +564,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D12" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/jui.jpg</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D13" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/aditiD.jpg</v>
       </c>
     </row>
     <row r="14">
@@ -606,7 +606,7 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D15" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/ketki.jpg</v>
       </c>
     </row>
     <row r="16">
@@ -676,12 +676,12 @@
         <v>Creative and Marketing Team</v>
       </c>
       <c r="D20" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/anuradha.jpg</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Snehshri</v>
+        <v>Snehsri</v>
       </c>
       <c r="B21" t="str">
         <v>Flyer Team</v>
@@ -788,7 +788,7 @@
         <v>Event Team</v>
       </c>
       <c r="D28" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/radhika.jpg</v>
       </c>
     </row>
     <row r="29">
@@ -830,7 +830,7 @@
         <v>Event Team</v>
       </c>
       <c r="D31" t="str">
-        <v>assets/images/team/</v>
+        <v>assets/images/team/madhura.jpg</v>
       </c>
     </row>
     <row r="32">
